--- a/app/reports/LMT_research.xlsx
+++ b/app/reports/LMT_research.xlsx
@@ -596,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-05-30 22:16 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-12 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.546</v>
+        <v>0.591</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>637.97</v>
+        <v>634.16</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>530.45</v>
+        <v>542.2975</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.203</v>
+        <v>0.169</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,71 +727,86 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.232</v>
+        <v>0.218</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>comps_percentile</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Peer-relative ranking of P/E, EV/EBITDA, EV/Rev</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>dcf_margin</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B15" s="9" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Normalized (intrinsic − market) / market, clipped ±50%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Honest caveats (read before acting)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
-        </is>
-      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
+          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
+          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
+          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>This is a SIGNAL screen, not an investment thesis. Verify with primary filings before acting.</t>
         </is>
@@ -801,6 +816,7 @@
   <mergeCells count="11">
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
@@ -809,7 +825,6 @@
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -876,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.0445300006866455</v>
+        <v>0.04479000091552734</v>
       </c>
     </row>
     <row r="6">
@@ -1205,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>230563619.9302479</v>
+        <v>230628461.8166228</v>
       </c>
     </row>
     <row r="36">
@@ -1226,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>530.45</v>
+        <v>542.2975</v>
       </c>
     </row>
     <row r="38">
@@ -1431,7 +1446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1505,92 +1520,266 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>122302472192</v>
+        <v>125069238272</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>25.71</v>
+        <v>26.29</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>17.65</v>
+        <v>18.18</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>90739679232</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>21.175373</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>14.419</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>4.232</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>The Boeing Company</t>
-        </is>
-      </c>
-      <c r="C6" s="33" t="n">
-        <v>182216007300</v>
-      </c>
-      <c r="D6" s="34" t="n">
-        <v>83.38744586891535</v>
-      </c>
-      <c r="E6" s="34" t="n">
-        <v>30.03604687329328</v>
-      </c>
-      <c r="F6" s="34" t="n">
-        <v>2.386357798533368</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Boeing Company (The)</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>174005911552</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <v>87.24704</v>
+      </c>
+      <c r="E7" s="34" t="n">
+        <v>-62.643</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>2.215</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Deere &amp; Company</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>155618934784</v>
+      </c>
+      <c r="D8" s="34" t="n">
+        <v>32.699944</v>
+      </c>
+      <c r="E8" s="34" t="n">
+        <v>22.422</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>4.08</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>General Dynamics Corporation</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>97333231616</v>
+      </c>
+      <c r="D9" s="34" t="n">
+        <v>22.636478</v>
+      </c>
+      <c r="E9" s="34" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <v>1.916</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Honeywell International Inc.</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="n">
+        <v>141520093184</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <v>35.620415</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>19.386</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <v>4.389</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LHX</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>L3Harris Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="n">
+        <v>57317367808</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <v>33.406082</v>
+      </c>
+      <c r="E11" s="34" t="n">
+        <v>35.455</v>
+      </c>
+      <c r="F11" s="34" t="n">
+        <v>5.918</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NOC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Northrop Grumman Corporation</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="n">
+        <v>78118412288</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <v>17.252195</v>
+      </c>
+      <c r="E12" s="34" t="n">
+        <v>12.859</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <v>2.218</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Parker-Hannifin Corporation</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="n">
+        <v>113327710208</v>
+      </c>
+      <c r="D13" s="34" t="n">
+        <v>33.20318</v>
+      </c>
+      <c r="E13" s="34" t="n">
+        <v>22.429</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <v>5.856</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Peer median</t>
         </is>
       </c>
-      <c r="D8" s="35">
-        <f>MEDIAN(D6:D6)</f>
-        <v/>
-      </c>
-      <c r="E8" s="35">
-        <f>MEDIAN(E6:E6)</f>
-        <v/>
-      </c>
-      <c r="F8" s="35">
-        <f>MEDIAN(F6:F6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="D15" s="35">
+        <f>MEDIAN(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E15" s="35">
+        <f>MEDIAN(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F15" s="35">
+        <f>MEDIAN(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Peer mean</t>
         </is>
       </c>
-      <c r="D9" s="35">
-        <f>AVERAGE(D6:D6)</f>
-        <v/>
-      </c>
-      <c r="E9" s="35">
-        <f>AVERAGE(E6:E6)</f>
-        <v/>
-      </c>
-      <c r="F9" s="35">
-        <f>AVERAGE(F6:F6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="D16" s="35">
+        <f>AVERAGE(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E16" s="35">
+        <f>AVERAGE(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F16" s="35">
+        <f>AVERAGE(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Target percentile vs peers</t>
         </is>
       </c>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="D17" s="36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E17" s="36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F17" s="36" t="n">
+        <v>0.167</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>(higher pct = more expensive than peers)</t>
         </is>

--- a/app/reports/LMT_research.xlsx
+++ b/app/reports/LMT_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-12 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-13 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.591</v>
+        <v>0.615</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>634.16</v>
+        <v>633</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>542.2975</v>
+        <v>540.33</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.169</v>
+        <v>0.172</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.218</v>
+        <v>0.221</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.7</v>
+        <v>0.756</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.669</v>
+        <v>0.672</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.04486999988555909</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>230628461.8166228</v>
+        <v>230563630.0186923</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>542.2975</v>
+        <v>540.33</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>125069238272</v>
+        <v>124580446208</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>26.29</v>
+        <v>26.18</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>18.18</v>
+        <v>17.93</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>90739679232</v>
+        <v>90423894016</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>21.175373</v>
+        <v>21.101679</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>14.419</v>
+        <v>14.447</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>4.232</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>174005911552</v>
+        <v>172677627904</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>87.24704</v>
+        <v>86.92461</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>-62.643</v>
+        <v>-62.019</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>2.215</v>
+        <v>2.193</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>155618934784</v>
+        <v>155883470848</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>32.699944</v>
+        <v>32.68138</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>22.422</v>
+        <v>22.699</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>4.08</v>
+        <v>4.131</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>97333231616</v>
+        <v>97414356992</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>22.636478</v>
+        <v>22.669603</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>15.89</v>
+        <v>15.947</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.916</v>
+        <v>1.922</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>141520093184</v>
+        <v>139600117760</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>35.620415</v>
+        <v>35.19329</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>19.386</v>
+        <v>19.474</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>4.389</v>
+        <v>4.409</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>57317367808</v>
+        <v>57339723776</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>33.406082</v>
+        <v>33.455437</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>35.455</v>
+        <v>35.004</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>5.918</v>
+        <v>5.843</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>78118412288</v>
+        <v>78165286912</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>17.252195</v>
+        <v>17.240915</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>12.859</v>
+        <v>12.816</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.218</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>113327710208</v>
+        <v>113916534784</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>33.20318</v>
+        <v>33.338745</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>22.429</v>
+        <v>22.455</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.856</v>
+        <v>5.862</v>
       </c>
     </row>
     <row r="15">
@@ -1775,7 +1775,7 @@
         <v>0.4</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">

--- a/app/reports/LMT_research.xlsx
+++ b/app/reports/LMT_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-13 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-14 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/LMT_research.xlsx
+++ b/app/reports/LMT_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-14 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-15 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.615</v>
+        <v>0.623</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>633</v>
+        <v>635.62</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>540.33</v>
+        <v>535.12</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.172</v>
+        <v>0.188</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.221</v>
+        <v>0.227</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.672</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04468999862670898</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>230563630.0186923</v>
+        <v>230563619.5544924</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>540.33</v>
+        <v>535.12</v>
       </c>
     </row>
     <row r="38">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>124580446208</v>
+        <v>123379204096</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>26.18</v>
+        <v>25.93</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>17.93</v>
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>90423894016</v>
+        <v>89776316416</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>21.101679</v>
+        <v>20.95056</v>
       </c>
       <c r="E6" s="34" t="n">
         <v>14.447</v>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>172677627904</v>
+        <v>181506605056</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>86.92461</v>
+        <v>91.36905</v>
       </c>
       <c r="E7" s="34" t="n">
         <v>-62.019</v>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>155883470848</v>
+        <v>157719052288</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>32.68138</v>
+        <v>33.066216</v>
       </c>
       <c r="E8" s="34" t="n">
         <v>22.699</v>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>97414356992</v>
+        <v>97661804544</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>22.669603</v>
+        <v>22.727186</v>
       </c>
       <c r="E9" s="34" t="n">
         <v>15.947</v>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>139600117760</v>
+        <v>145499488256</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>35.19329</v>
+        <v>36.680527</v>
       </c>
       <c r="E10" s="34" t="n">
         <v>19.474</v>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>57339723776</v>
+        <v>56715632640</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>33.455437</v>
+        <v>33.091305</v>
       </c>
       <c r="E11" s="34" t="n">
         <v>35.004</v>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>78165286912</v>
+        <v>77274726400</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>17.240915</v>
+        <v>17.044487</v>
       </c>
       <c r="E12" s="34" t="n">
         <v>12.816</v>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>113916534784</v>
+        <v>117098946560</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>33.338745</v>
+        <v>34.270107</v>
       </c>
       <c r="E13" s="34" t="n">
         <v>22.455</v>

--- a/app/reports/LMT_research.xlsx
+++ b/app/reports/LMT_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-15 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-16 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.623</v>
+        <v>0.625</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>635.62</v>
+        <v>641.96</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>535.12</v>
+        <v>537.1</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.188</v>
+        <v>0.195</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.227</v>
+        <v>0.224</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.695</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04468999862670898</v>
+        <v>0.04425999641418457</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>230563619.5544924</v>
+        <v>230563603.5896481</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>535.12</v>
+        <v>537.1</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>123379204096</v>
+        <v>123835711488</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>25.93</v>
+        <v>26.03</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>17.93</v>
+        <v>17.65</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>89776316416</v>
+        <v>88243339264</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>20.95056</v>
+        <v>20.612045</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>14.447</v>
+        <v>14.259</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>4.24</v>
+        <v>4.185</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>181506605056</v>
+        <v>180265041920</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>91.36905</v>
+        <v>90.02952999999999</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>-62.019</v>
+        <v>-64.414</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>2.193</v>
+        <v>2.277</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>157719052288</v>
+        <v>158161747968</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>33.066216</v>
+        <v>33.159027</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>22.699</v>
+        <v>22.636</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>4.131</v>
+        <v>4.119</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>97661804544</v>
+        <v>98628583424</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>22.727186</v>
+        <v>22.95217</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>15.947</v>
+        <v>15.918</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.922</v>
+        <v>1.919</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>145499488256</v>
+        <v>146164760576</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>36.680527</v>
+        <v>36.9072</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>19.474</v>
+        <v>20.002</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>4.409</v>
+        <v>4.528</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>56715632640</v>
+        <v>57717899264</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>33.091305</v>
+        <v>33.603035</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>35.004</v>
+        <v>34.631</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>5.843</v>
+        <v>5.781</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>77274726400</v>
+        <v>78491959296</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>17.044487</v>
+        <v>17.31297</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>12.816</v>
+        <v>12.708</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.21</v>
+        <v>2.192</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>117098946560</v>
+        <v>118654861312</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>34.270107</v>
+        <v>34.71265</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>22.455</v>
+        <v>22.809</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.862</v>
+        <v>5.955</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/LMT_research.xlsx
+++ b/app/reports/LMT_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-16 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-17 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.625</v>
+        <v>0.627</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>641.96</v>
+        <v>641.0700000000001</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>537.1</v>
+        <v>534.65</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.195</v>
+        <v>0.199</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.224</v>
+        <v>0.227</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.695</v>
+        <v>0.699</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04425999641418457</v>
+        <v>0.04432000160217285</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>230563603.5896481</v>
+        <v>230542048.038904</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>537.1</v>
+        <v>534.65</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>123835711488</v>
+        <v>123259305984</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>26.03</v>
+        <v>25.91</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>17.65</v>
+        <v>17.81</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>88243339264</v>
+        <v>88253333504</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>20.612045</v>
+        <v>20.595148</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>14.259</v>
+        <v>14.182</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>4.185</v>
+        <v>4.162</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>180265041920</v>
+        <v>181218885632</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>90.02952999999999</v>
+        <v>90.86363</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>-64.414</v>
+        <v>-64.06</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>2.277</v>
+        <v>2.265</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>158161747968</v>
+        <v>160363085824</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>33.159027</v>
+        <v>33.60153</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>22.636</v>
+        <v>22.944</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>4.119</v>
+        <v>4.175</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>98628583424</v>
+        <v>98826002432</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>22.95217</v>
+        <v>22.712244</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>15.918</v>
+        <v>16.109</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.919</v>
+        <v>1.942</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>146164760576</v>
+        <v>147400392704</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>36.9072</v>
+        <v>37.10048</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>20.002</v>
+        <v>20.157</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>4.528</v>
+        <v>4.563</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>57717899264</v>
+        <v>58978185216</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>33.603035</v>
+        <v>34.336765</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>34.631</v>
+        <v>35.278</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>5.781</v>
+        <v>5.889</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>78491959296</v>
+        <v>78682275840</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>17.31297</v>
+        <v>17.354948</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>12.708</v>
+        <v>12.833</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.192</v>
+        <v>2.213</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>118654861312</v>
+        <v>120636940288</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>34.71265</v>
+        <v>35.2795</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>22.809</v>
+        <v>23.261</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.955</v>
+        <v>6.073</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/LMT_research.xlsx
+++ b/app/reports/LMT_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-17 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.627</v>
+        <v>0.651</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>641.0700000000001</v>
+        <v>618.8200000000001</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>534.65</v>
+        <v>574.625</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.199</v>
+        <v>0.077</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.227</v>
+        <v>0.346</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.756</v>
+        <v>0.878</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.699</v>
+        <v>0.577</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04432000160217285</v>
+        <v>0.04647000312805176</v>
       </c>
     </row>
     <row r="6">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>20696999936</v>
+        <v>20537999360</v>
       </c>
     </row>
     <row r="33">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1894000000</v>
+        <v>3791000064</v>
       </c>
     </row>
     <row r="34">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>230542048.038904</v>
+        <v>230790747.8860126</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>534.65</v>
+        <v>574.625</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>123259305984</v>
+        <v>132618133504</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>25.91</v>
+        <v>21.16</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>17.81</v>
+        <v>15.59</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>88253333504</v>
+        <v>111082160128</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>20.595148</v>
+        <v>25.898418</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>14.182</v>
+        <v>16.841</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>4.162</v>
+        <v>4.943</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>181218885632</v>
+        <v>170259513344</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>90.86363</v>
+        <v>85.20751</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>-64.06</v>
+        <v>-60.193</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>2.265</v>
+        <v>2.128</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>160363085824</v>
+        <v>166659375104</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>33.60153</v>
+        <v>34.960365</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>22.944</v>
+        <v>24.653</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>4.175</v>
+        <v>4.486</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>98826002432</v>
+        <v>105751715840</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>22.712244</v>
+        <v>24.625315</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>16.109</v>
+        <v>17.319</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.942</v>
+        <v>2.088</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>147400392704</v>
+        <v>76784738304</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>37.10048</v>
+        <v>9.314456</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>20.157</v>
+        <v>12.263</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>4.563</v>
+        <v>2.743</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>58978185216</v>
+        <v>55778324480</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>34.336765</v>
+        <v>32.473827</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>35.278</v>
+        <v>34.737</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>5.889</v>
+        <v>5.799</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>78682275840</v>
+        <v>77430030336</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>17.354948</v>
+        <v>17.319351</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>12.833</v>
+        <v>12.787</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.213</v>
+        <v>2.163</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>120636940288</v>
+        <v>119963009024</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>35.2795</v>
+        <v>35.1732</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>23.261</v>
+        <v>24.468</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>6.073</v>
+        <v>6.388</v>
       </c>
     </row>
     <row r="15">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F17" s="36" t="n">
         <v>0</v>

--- a/app/reports/LMT_research.xlsx
+++ b/app/reports/LMT_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-31 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.651</v>
+        <v>0.638</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>618.8200000000001</v>
+        <v>606.79</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>574.625</v>
+        <v>579.595</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.077</v>
+        <v>0.047</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.346</v>
+        <v>0.34</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.577</v>
+        <v>0.547</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04647000312805176</v>
+        <v>0.04736999988555908</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>230790747.8860126</v>
+        <v>230790743.4674212</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>574.625</v>
+        <v>579.595</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>132618133504</v>
+        <v>133765160960</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>21.16</v>
+        <v>21.39</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>15.59</v>
+        <v>15.42</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>111082160128</v>
+        <v>105478660096</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>25.898418</v>
+        <v>24.215069</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>16.841</v>
+        <v>16.603</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>4.943</v>
+        <v>4.836</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>170259513344</v>
+        <v>170115301376</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>85.20751</v>
+        <v>77.42265999999999</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>-60.193</v>
+        <v>-70.235</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>2.128</v>
+        <v>2.167</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>166659375104</v>
+        <v>160674856960</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>34.960365</v>
+        <v>33.781494</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>24.653</v>
+        <v>23.388</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>4.486</v>
+        <v>4.256</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>105751715840</v>
+        <v>103554408448</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>24.625315</v>
+        <v>23.33811</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>17.319</v>
+        <v>16.342</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>2.088</v>
+        <v>1.976</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>76784738304</v>
+        <v>77651886080</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>9.314456</v>
+        <v>9.419646</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>12.263</v>
+        <v>12.071</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>2.743</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>55778324480</v>
+        <v>51790925824</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>32.473827</v>
+        <v>28.081314</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>34.737</v>
+        <v>31.307</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>5.799</v>
+        <v>5.226</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>77430030336</v>
+        <v>76980404224</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>17.319351</v>
+        <v>17.229729</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>12.787</v>
+        <v>12.506</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.163</v>
+        <v>2.115</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>119963009024</v>
+        <v>122863624192</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>35.1732</v>
+        <v>36.023663</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>24.468</v>
+        <v>23.82</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>6.388</v>
+        <v>6.219</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/LMT_research.xlsx
+++ b/app/reports/LMT_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-31 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-01 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.638</v>
+        <v>0.634</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>606.79</v>
+        <v>605.74</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>579.595</v>
+        <v>582.74</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.047</v>
+        <v>0.039</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.34</v>
+        <v>0.337</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.547</v>
+        <v>0.539</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04736999988555908</v>
+        <v>0.04744999885559082</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>230790743.4674212</v>
+        <v>230790741.5588427</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>579.595</v>
+        <v>582.74</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>133765160960</v>
+        <v>134490996736</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>21.39</v>
+        <v>21.5</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>15.42</v>
+        <v>15.62</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>105478660096</v>
+        <v>105997787136</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>24.215069</v>
+        <v>24.334246</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>16.603</v>
+        <v>16.764</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>4.836</v>
+        <v>4.883</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>170115301376</v>
+        <v>170830577664</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>77.42265999999999</v>
+        <v>77.46953600000001</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>-70.235</v>
+        <v>-68.937</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>2.167</v>
+        <v>2.127</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>160674856960</v>
+        <v>159983812608</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>33.781494</v>
+        <v>33.56002</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>23.388</v>
+        <v>23.175</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>4.256</v>
+        <v>4.217</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>103554408448</v>
+        <v>103737040896</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>23.33811</v>
+        <v>23.365023</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>16.342</v>
+        <v>16.392</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.976</v>
+        <v>1.982</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>77651886080</v>
+        <v>77032267776</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>9.419646</v>
+        <v>9.344483</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>12.071</v>
+        <v>12.114</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>2.7</v>
+        <v>2.709</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>51790925824</v>
+        <v>51592622080</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>28.081314</v>
+        <v>28.014154</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>31.307</v>
+        <v>31.838</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>5.226</v>
+        <v>5.315</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>76980404224</v>
+        <v>77066346496</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>17.229729</v>
+        <v>17.243484</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>12.506</v>
+        <v>12.655</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.115</v>
+        <v>2.141</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>122863624192</v>
+        <v>123127144448</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>36.023663</v>
+        <v>35.967957</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>23.82</v>
+        <v>24.136</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>6.219</v>
+        <v>6.301</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/LMT_research.xlsx
+++ b/app/reports/LMT_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-01 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-07 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.634</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>605.74</v>
+        <v>600.67</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>582.74</v>
+        <v>525.28</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.039</v>
+        <v>0.144</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.337</v>
+        <v>0.39</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.539</v>
+        <v>0.644</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.04783999919891357</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>230790741.5588427</v>
+        <v>230790760.6457509</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>582.74</v>
+        <v>525.28</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>134490996736</v>
+        <v>121229770752</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>21.5</v>
+        <v>19.38</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>15.62</v>
+        <v>14.25</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>105997787136</v>
+        <v>110288084992</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>24.334246</v>
+        <v>25.3766</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>16.764</v>
+        <v>17.403</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>4.883</v>
+        <v>5.084</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>170830577664</v>
+        <v>167756038144</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>77.46953600000001</v>
+        <v>76.34892000000001</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>-68.937</v>
+        <v>-67.877</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>2.127</v>
+        <v>2.094</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>159983812608</v>
+        <v>186993311744</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>33.56002</v>
+        <v>38.61526</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>23.175</v>
+        <v>26.353</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>4.217</v>
+        <v>4.729</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>103737040896</v>
+        <v>97235550208</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>23.365023</v>
+        <v>21.927397</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>16.392</v>
+        <v>15.413</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.982</v>
+        <v>1.864</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>77032267776</v>
+        <v>66433794048</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>9.344483</v>
+        <v>8.058824</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>12.114</v>
+        <v>10.869</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>2.709</v>
+        <v>2.431</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>51592622080</v>
+        <v>47754743808</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>28.014154</v>
+        <v>25.904043</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>31.838</v>
+        <v>29.715</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>5.315</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>77066346496</v>
+        <v>73159614464</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>17.243484</v>
+        <v>16.364157</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>12.655</v>
+        <v>12.116</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.141</v>
+        <v>2.049</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>123127144448</v>
+        <v>121332039680</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>35.967957</v>
+        <v>33.786945</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>24.136</v>
+        <v>22.877</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>6.301</v>
+        <v>6.027</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/LMT_research.xlsx
+++ b/app/reports/LMT_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-07 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-11 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>600.67</v>
+        <v>580.29</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>525.28</v>
+        <v>525.74</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.144</v>
+        <v>0.104</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.39</v>
+        <v>0.391</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.644</v>
+        <v>0.604</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.04947000026702881</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>230790760.6457509</v>
+        <v>230790753.7566097</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>525.28</v>
+        <v>525.74</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>121229770752</v>
+        <v>121335930880</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>19.38</v>
+        <v>19.37</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>14.25</v>
+        <v>14.37</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>110288084992</v>
+        <v>106100932608</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>25.3766</v>
+        <v>24.435497</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>17.403</v>
+        <v>16.765</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>5.084</v>
+        <v>4.897</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>167756038144</v>
+        <v>166602096640</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>76.34892000000001</v>
+        <v>75.55197</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>-67.877</v>
+        <v>-65.84699999999999</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>2.094</v>
+        <v>2.032</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>186993311744</v>
+        <v>184032821248</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>38.61526</v>
+        <v>37.98275</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>26.353</v>
+        <v>25.865</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>4.729</v>
+        <v>4.641</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>97235550208</v>
+        <v>96560504832</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>21.927397</v>
+        <v>21.76189</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>15.413</v>
+        <v>15.204</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.864</v>
+        <v>1.838</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>66433794048</v>
+        <v>64373682176</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>8.058824</v>
+        <v>7.811923</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>10.869</v>
+        <v>10.592</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>2.431</v>
+        <v>2.369</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>47754743808</v>
+        <v>45922390016</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>25.904043</v>
+        <v>24.884966</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>29.715</v>
+        <v>28.883</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>4.96</v>
+        <v>4.821</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>73159614464</v>
+        <v>73999212544</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>16.364157</v>
+        <v>16.56248</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>12.116</v>
+        <v>12.194</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.049</v>
+        <v>2.063</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>121332039680</v>
+        <v>119645003776</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>33.786945</v>
+        <v>33.30547</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>22.877</v>
+        <v>22.248</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>6.027</v>
+        <v>5.861</v>
       </c>
     </row>
     <row r="15">
